--- a/translation/review/000scriptAKYO_0032T.xlsx
+++ b/translation/review/000scriptAKYO_0032T.xlsx
@@ -16,7 +16,7 @@
     <t>The True Little Sister Showdown : Siscalypse</t>
   </si>
   <si>
-    <t>El Verdadero Enfrentamiento de Hermanitas: Siscalipse</t>
+    <t>El Verdadero Enfrentamiento de Hermanitas:＿Siscalipse</t>
   </si>
   <si>
     <t>Kirino</t>
@@ -40,7 +40,7 @@
     <t>Hey, you. Do you understand the position that you're in right now?</t>
   </si>
   <si>
-    <t>Oye, tú. ¿Entiendes la posición en la que estás ahora mismo?</t>
+    <t>Oye, tú. ¿Entiendes la posición en la que estás＿ahora mismo?</t>
   </si>
   <si>
     <t>My position?</t>
@@ -52,13 +52,13 @@
     <t>I'll tell you once more since you don't seem to get it.</t>
   </si>
   <si>
-    <t>Te lo diré una vez más ya que no parece que lo entiendas.</t>
+    <t>Te lo diré una vez más ya que no parece que lo＿entiendas.</t>
   </si>
   <si>
     <t>All you need to do is listen to whatever I say. Are you all right?</t>
   </si>
   <si>
-    <t>Todo lo que necesitas hacer es escuchar lo que diga. ¿Está claro?</t>
+    <t>Todo lo que necesitas hacer es escuchar lo que＿diga. ¿Está claro?</t>
   </si>
   <si>
     <t>Yes, understand!</t>
@@ -76,13 +76,13 @@
     <t>Your pronunciation sucks, it's on a dropout's level.</t>
   </si>
   <si>
-    <t>Tu pronunciación apesta, está a nivel de un fracasado.</t>
+    <t>Tu pronunciación apesta, está a nivel de un＿fracasado.</t>
   </si>
   <si>
     <t>Dropout is a taboo word for someone taking his exams this year!</t>
   </si>
   <si>
-    <t>¡Fracasado es una palabra tabú para alguien que se examina este año!</t>
+    <t>¡Fracasado es una palabra tabú para alguien que＿se examina este año!</t>
   </si>
   <si>
     <t>Hah...</t>
@@ -121,7 +121,7 @@
     <t>I mean, thanks to me, you'll be able to join the tournament...</t>
   </si>
   <si>
-    <t>Quiero decir, gracias a mí, podrás unirte al torneo...</t>
+    <t>Quiero decir, gracias a mí, podrás unirte al＿torneo...</t>
   </si>
   <si>
     <t>You could show some gratitude.</t>
@@ -139,7 +139,7 @@
     <t>Eh? Even though I arranged this so friendless you could have social interactions.</t>
   </si>
   <si>
-    <t>¿Eh? Aunque organicé esto para que tú, sin amigos, pudieras tener interacciones sociales.</t>
+    <t>¿Eh? Aunque organicé esto para que tú, sin＿amigos, pudieras tener interacciones sociales.</t>
   </si>
   <si>
     <t>I do! I definitely do have friends!</t>
@@ -151,19 +151,19 @@
     <t>And stop with that "Lies, I'm super-shocked" face! Even my feelings can be hurt!</t>
   </si>
   <si>
-    <t>¡Y deja esa cara de «Mentira, estoy súper sorprendido»! ¡Incluso mis sentimientos pueden herirse!</t>
+    <t>¡Y deja esa cara de «Mentira, estoy súper＿sorprendido»! ¡Incluso mis sentimientos＿pueden herirse!</t>
   </si>
   <si>
     <t>Furthermore, are there any benefits for me by participating in this tournament?</t>
   </si>
   <si>
-    <t>Además, ¿hay algún beneficio para mí al participar en este torneo?</t>
+    <t>Además, ¿hay algún beneficio para mí al＿participar en este torneo?</t>
   </si>
   <si>
     <t>If you win, I will be happy. If your cute little sister is happy, you will be happy as well!</t>
   </si>
   <si>
-    <t>Si ganas, seré feliz. Si tu linda hermanita es feliz, tú también serás feliz!</t>
+    <t>Si ganas, seré feliz. Si tu linda hermanita es feliz,＿tú también serás feliz!</t>
   </si>
   <si>
     <t>...You say some dreadful things sometimes.</t>
@@ -181,7 +181,7 @@
     <t>Aren't you happy? To be together with such a cute girl! it's quite a rare chance.</t>
   </si>
   <si>
-    <t>¿No eres feliz? Estar junto a una chica tan linda. Es una oportunidad bastante rara.</t>
+    <t>¿No eres feliz? Estar junto a una chica tan linda.＿Es una oportunidad bastante rara.</t>
   </si>
   <si>
     <t>Don't say that about yourself.</t>
@@ -193,19 +193,19 @@
     <t>Anyway, you're going to join the Siscaly game tournament.</t>
   </si>
   <si>
-    <t>De todos modos, vas a unirte al torneo del juego Siscaly.</t>
+    <t>De todos modos, vas a unirte al torneo del＿juego Siscaly.</t>
   </si>
   <si>
     <t>You will have to be able to win at least 30 consecutive rounds before the tournament. That's the norm.</t>
   </si>
   <si>
-    <t>Tendrás que poder ganar al menos 30 rondas consecutivas antes del torneo. Esa es la norma.</t>
+    <t>Tendrás que poder ganar al menos 30 rondas＿consecutivas antes del torneo. Esa es la norma.</t>
   </si>
   <si>
     <t>30 consecutive rounds?! Impossible! Totaaally impossible!!</t>
   </si>
   <si>
-    <t>¡¿30 rondas consecutivas?! ¡Imposible! ¡Totaalmente imposible!!</t>
+    <t>¡¿30 rondas consecutivas?! ¡Imposible!＿¡Totaalmente imposible!!</t>
   </si>
   <si>
     <t>Why are you giving up before you've even started?</t>
@@ -217,7 +217,7 @@
     <t>No matter what you say, impossible is impossible!</t>
   </si>
   <si>
-    <t>No importa lo que digas, ¡imposible es imposible!</t>
+    <t>No importa lo que digas, ¡imposible es＿imposible!</t>
   </si>
   <si>
     <t>That's why! You have to practice!</t>
@@ -229,19 +229,19 @@
     <t>Even if we are strong, you'll do more harm than good if you drag us down.</t>
   </si>
   <si>
-    <t>Incluso si somos fuertes, harás más daño que bien si nos arrastras.</t>
+    <t>Incluso si somos fuertes, harás más daño que＿bien si nos arrastras.</t>
   </si>
   <si>
     <t>Excluding myself, out of the three others, you suck the most!</t>
   </si>
   <si>
-    <t>¡Excluyéndome a mí, de las otras tres, tú apestas más!</t>
+    <t>¡Excluyéndome a mí, de las otras tres, tú apestas＿más!</t>
   </si>
   <si>
     <t>...I think it's impossible... Your request is simply too unrealistic...</t>
   </si>
   <si>
-    <t>...Creo que es imposible... Tu petición es simplemente demasiado irreal...</t>
+    <t>...Creo que es imposible... Tu petición es＿simplemente demasiado irreal...</t>
   </si>
   <si>
     <t>Don't say that you can't do it.</t>
@@ -253,13 +253,13 @@
     <t>By the way, I will be having my exams this year and I won't have time to do this, get it?</t>
   </si>
   <si>
-    <t>Por cierto, tendré mis exámenes este año y no tendré tiempo para esto, ¿me entiendes?</t>
+    <t>Por cierto, tendré mis exámenes este año y no＿tendré tiempo para esto, ¿me entiendes?</t>
   </si>
   <si>
     <t>Then just make some time. Don't you want to play with me?</t>
   </si>
   <si>
-    <t>Entonces solo haz tiempo. ¿No quieres jugar conmigo?</t>
+    <t>Entonces solo haz tiempo. ¿No quieres jugar＿conmigo?</t>
   </si>
   <si>
     <t>Besides, this is inevitable.</t>
@@ -277,13 +277,13 @@
     <t>It has been decided ever since you were born into this world!</t>
   </si>
   <si>
-    <t>¡Ha sido decidido desde que naciste en este mundo!</t>
+    <t>¡Ha sido decidido desde que naciste en este＿mundo!</t>
   </si>
   <si>
     <t>Already decided?! Don't I have a right to object?!</t>
   </si>
   <si>
-    <t>¡¿Ya está decidido?! ¡¿No tengo derecho a oponerme?!</t>
+    <t>¡¿Ya está decidido?! ¡¿No tengo derecho a＿oponerme?!</t>
   </si>
   <si>
     <t>Of course not.</t>
